--- a/Telegram/Data.xlsx
+++ b/Telegram/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42000ae913e9c605/Máy tính/EAForex/Telegram/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="11_F25DC773A252ABDACC10487D599D7F465BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEAEB2B6-113D-43E9-A9A1-215CD644DFCE}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="11_F25DC773A252ABDACC10487D599D7F465BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02C989A8-F8B7-4E8B-9BEF-678F47F088D1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,22 +36,22 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
-    <t>api_id</t>
-  </si>
-  <si>
-    <t>api_hash</t>
-  </si>
-  <si>
-    <t>source_id</t>
-  </si>
-  <si>
-    <t>destination_ids</t>
-  </si>
-  <si>
     <t>a6e00e485b0c1ddf905b13f7d9fe1b3e</t>
   </si>
   <si>
     <t>-5101501820, -5162765052</t>
+  </si>
+  <si>
+    <t>Mã_API</t>
+  </si>
+  <si>
+    <t>Chuỗi_API</t>
+  </si>
+  <si>
+    <t>ID_Nguồn</t>
+  </si>
+  <si>
+    <t>Danh_Sách_ID_Nhận</t>
   </si>
 </sst>
 </file>
@@ -411,16 +411,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -428,13 +428,13 @@
         <v>26845740</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C2" s="2">
         <v>-5185439945</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Telegram/Data.xlsx
+++ b/Telegram/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42000ae913e9c605/Máy tính/EAForex/Telegram/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="11_F25DC773A252ABDACC10487D599D7F465BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02C989A8-F8B7-4E8B-9BEF-678F47F088D1}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="11_F25DC773A252ABDACC10487D599D7F465BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7784756-5D03-400A-9990-A31003CA2A32}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>a6e00e485b0c1ddf905b13f7d9fe1b3e</t>
   </si>
@@ -52,6 +52,15 @@
   </si>
   <si>
     <t>Danh_Sách_ID_Nhận</t>
+  </si>
+  <si>
+    <t>Ngon_Nguu_Goc</t>
+  </si>
+  <si>
+    <t>Ngon_Nguu_Dich</t>
+  </si>
+  <si>
+    <t>vi</t>
   </si>
 </sst>
 </file>
@@ -400,16 +409,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" customWidth="1"/>
     <col min="2" max="2" width="43.7109375" customWidth="1"/>
     <col min="3" max="3" width="22.28515625" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -422,8 +433,14 @@
       <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>26845740</v>
       </c>
@@ -435,6 +452,12 @@
       </c>
       <c r="D2" s="3" t="s">
         <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Telegram/Data.xlsx
+++ b/Telegram/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42000ae913e9c605/Máy tính/EAForex/Telegram/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="11_F25DC773A252ABDACC10487D599D7F465BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7784756-5D03-400A-9990-A31003CA2A32}"/>
+  <xr:revisionPtr revIDLastSave="119" documentId="11_F25DC773A252ABDACC10487D599D7F465BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61EBA435-90D4-4A5E-9B49-AD5DA7D2C827}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,13 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
-  <si>
-    <t>a6e00e485b0c1ddf905b13f7d9fe1b3e</t>
-  </si>
-  <si>
-    <t>-5101501820, -5162765052</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>Mã_API</t>
   </si>
@@ -62,12 +56,151 @@
   <si>
     <t>vi</t>
   </si>
+  <si>
+    <t xml:space="preserve">Tiếng Việt: vi
+Tiếng Anh: en
+Tiếng Trung (Giản thể): zh-CN
+Tiếng Nhật: ja
+Tiếng Hàn: ko
+Tiếng Pháp: fr
+Tiếng Đức: de
+Tiếng Nga: ru                                                                              </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bước 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Truy cập và Đăng nhập
+Truy cập địa chỉ: https://my.telegram.org.
+Nhập Số điện thoại của bạn (định dạng quốc tế, ví dụ: +84901234567).
+Telegram sẽ gửi một mã xác nhận vào ứng dụng Telegram trên điện thoại/máy tính của bạn (không phải qua SMS). Nhập mã đó vào web để đăng nhập.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bước 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Tạo ứng dụng (Ứng dụng ví dụ)
+Sau khi đăng nhập, chọn dòng API development tools. Bạn sẽ thấy một biểu mẫu. Hãy điền như ví dụ sau:
+App title: Đặt tên bất kỳ (Ví dụ: My Forwarder Bot).
+Short name: Viết liền, không dấu (Ví dụ: my_forward_bot).
+URL: Bạn có thể để trống hoặc điền https://localhost.
+Platform: Chọn Desktop (hoặc Android/iOS đều được, không quan trọng lắm).
+Description: Có thể để trống.
+Nhấn nút Create application.
+Bước 3: Lấy thông tin
+Sau khi nhấn tạo, màn hình sẽ hiện ra thông tin cấu hình. Bạn chỉ cần quan tâm 2 dòng:
+App api_id: Một dãy số (Ví dụ: 28471923).
+App api_hash: Một dãy gồm chữ và số (Ví dụ: a1b2c3d4e5f6...).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[!IMPORTANT]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Lưu ý bảo mật: Đừng chia sẻ api_hash cho bất kỳ ai. Nếu ai đó có cả 2 thông tin này, họ có thể đăng nhập vào tài khoản Telegram của bạn thông qua code.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bước 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Tìm kiếm bot có tên @userinfobot hoặc @MissRose_bot trên Telegram.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Bước 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Đối với ID cá nhân: Chỉ cần nhấn /start, bot sẽ trả về ID của bạn.
+Đối với ID Nhóm/Kênh: * Hãy Forward (Chuyển tiếp) một tin nhắn bất kỳ từ nhóm/kênh đó vào bot này.
+Bot sẽ hiển thị thông tin chi tiết bao gồm Forwarded from chat: [Tên nhóm] (ID: -100xxxxxxxxxx).</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -81,6 +214,14 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -118,12 +259,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -409,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" customWidth="1"/>
@@ -422,45 +567,352 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>26845740</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2">
-        <v>-5185439945</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="F3" s="5"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="5"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="5"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="5"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="5"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="5"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="5"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="5"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:B40"/>
+    <mergeCell ref="C3:D40"/>
+    <mergeCell ref="E3:F40"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Telegram/Data.xlsx
+++ b/Telegram/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42000ae913e9c605/Máy tính/EAForex/Telegram/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="119" documentId="11_F25DC773A252ABDACC10487D599D7F465BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61EBA435-90D4-4A5E-9B49-AD5DA7D2C827}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="11_F25DC773A252ABDACC10487D599D7F465BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B947580-3F73-47BC-9072-44D580FCB839}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,143 +57,13 @@
     <t>vi</t>
   </si>
   <si>
-    <t xml:space="preserve">Tiếng Việt: vi
-Tiếng Anh: en
-Tiếng Trung (Giản thể): zh-CN
-Tiếng Nhật: ja
-Tiếng Hàn: ko
-Tiếng Pháp: fr
-Tiếng Đức: de
-Tiếng Nga: ru                                                                              </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Bước 1:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Truy cập và Đăng nhập
-Truy cập địa chỉ: https://my.telegram.org.
-Nhập Số điện thoại của bạn (định dạng quốc tế, ví dụ: +84901234567).
-Telegram sẽ gửi một mã xác nhận vào ứng dụng Telegram trên điện thoại/máy tính của bạn (không phải qua SMS). Nhập mã đó vào web để đăng nhập.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Bước 2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Tạo ứng dụng (Ứng dụng ví dụ)
-Sau khi đăng nhập, chọn dòng API development tools. Bạn sẽ thấy một biểu mẫu. Hãy điền như ví dụ sau:
-App title: Đặt tên bất kỳ (Ví dụ: My Forwarder Bot).
-Short name: Viết liền, không dấu (Ví dụ: my_forward_bot).
-URL: Bạn có thể để trống hoặc điền https://localhost.
-Platform: Chọn Desktop (hoặc Android/iOS đều được, không quan trọng lắm).
-Description: Có thể để trống.
-Nhấn nút Create application.
-Bước 3: Lấy thông tin
-Sau khi nhấn tạo, màn hình sẽ hiện ra thông tin cấu hình. Bạn chỉ cần quan tâm 2 dòng:
-App api_id: Một dãy số (Ví dụ: 28471923).
-App api_hash: Một dãy gồm chữ và số (Ví dụ: a1b2c3d4e5f6...).
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[!IMPORTANT]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Lưu ý bảo mật: Đừng chia sẻ api_hash cho bất kỳ ai. Nếu ai đó có cả 2 thông tin này, họ có thể đăng nhập vào tài khoản Telegram của bạn thông qua code.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Bước 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Tìm kiếm bot có tên @userinfobot hoặc @MissRose_bot trên Telegram.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Bước 2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Đối với ID cá nhân: Chỉ cần nhấn /start, bot sẽ trả về ID của bạn.
-Đối với ID Nhóm/Kênh: * Hãy Forward (Chuyển tiếp) một tin nhắn bất kỳ từ nhóm/kênh đó vào bot này.
-Bot sẽ hiển thị thông tin chi tiết bao gồm Forwarded from chat: [Tên nhóm] (ID: -100xxxxxxxxxx).</t>
-    </r>
+    <t>a6e00e485b0c1ddf905b13f7d9fe1b3e</t>
+  </si>
+  <si>
+    <t>-5185439945</t>
+  </si>
+  <si>
+    <t>-5101501820</t>
   </si>
 </sst>
 </file>
@@ -216,12 +86,10 @@
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -263,13 +131,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -585,11 +451,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="3"/>
+    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>26845740</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
@@ -598,321 +472,310 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="5"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="5"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="5"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="5"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="5"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="5"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A3:B40"/>
-    <mergeCell ref="C3:D40"/>
-    <mergeCell ref="E3:F40"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
